--- a/data/trans_bre/IP18E_R1-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18E_R1-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-20,47</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-21,96%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>5.343330319474749</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.957146188736193</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.418207116196259</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-20.46779442584413</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.06577193813775609</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.03406691330355826</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.04001011973530112</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2196108454335407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,46; 13,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,6; 10,94</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 11,81</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-38,23; -0,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; 17,61</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-5,23; 13,45</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 15,13</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-39,86; -1,77</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.46220977187099</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.600110856250536</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.089202983243062</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-38.22530501613743</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.03943196194409299</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.05234376734477184</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.0454594951530724</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3986004105036365</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.15236543468034</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.94237985829337</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.80834808549855</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-0.603275543494016</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1760557755487845</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1345003802535489</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1513039441018658</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-0.01771419336001139</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,32</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-25,56</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,25%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-2,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-31,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-9,41; 6,11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-12,07; 2,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,56; 5,41</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-56,52; 4,06</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-10,1; 6,96</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-12,95; 3,12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-10,37; 6,35</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-65,4; 4,59</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.049058479666521</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.320356723793106</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.187021388542576</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-25.56417577579392</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.02246542584812244</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04737449659386517</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.02473197752281867</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3142541299915626</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-9.411682541714001</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-12.07164906472988</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.56376130064189</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-56.52068882148911</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1010027180472633</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1294867142798685</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1037041967224783</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6539670938749094</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,26; 8,22</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 2,93</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 8,87</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,87</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 9,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-5,5; 3,09</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 10,05</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 40,53</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.107401722024832</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.869095621463633</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.40828033404155</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.060861771486507</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06959030323562303</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03121622287476861</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.06352620048675429</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.04594195561256226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.351685695329753</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.9513394885643289</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.109617559802623</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.573845893443008</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.02503183729081036</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.009763621180610995</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.02280651346535028</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.05902862343787819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,18; 2,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,24; 4,7</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,24; 0,77</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 10,84</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,37; 2,3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-2,3; 5,09</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 0,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 12,4</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.259445408442873</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.451539359927389</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.684007744151462</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.04405462532276522</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.05502859093510042</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.0485692890551096</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.221961011156072</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.933379013328224</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.868400446702532</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>28.87483792023482</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.09134400313324983</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.0309294941658322</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1005262643926472</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4053213669232598</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,76; 2,93</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 1,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,68; 2,97</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-18,68; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 3,02</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-2,72; 1,57</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 3,07</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,68; 0,0</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.276893696178205</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.223185945498106</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.081555718888539</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.955509296445124</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.01334208463561108</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.01290586063070353</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02134315539988224</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.02088220706701763</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-2,37</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-2,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.178923240015921</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.235499766204367</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.242432856347184</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.194841887446415</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.0537441848534153</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.02302017642548413</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.05320525500459107</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.06324141602572163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-4,74; 8,51</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,33; 1,5</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-8,43; 1,4</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-12,06; 18,27</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-4,89; 9,74</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-8,4; 1,54</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-8,54; 1,37</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-12,69; 22,59</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.187030807831746</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.698532425514551</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.7733089218073367</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10.8401308697671</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02301684865033365</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0508797386431294</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.007913615746892125</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1240187755644578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-7,56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-0,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-8,09%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.1277791983240406</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.154696898863993</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.4710784944625179</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.789038567365256</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.001296801092013813</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.001562392095988005</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.004784965514066996</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.04789038567365256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,3; 2,65</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,23; 1,87</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,29; 1,77</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-14,9; -1,22</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,46; 2,91</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-2,32; 1,99</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-2,43; 1,89</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-15,65; -1,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.756194325511059</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.689786327119088</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.682782952737332</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-18.676824180302</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02794190409277668</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.02721756151783591</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.01695974290609857</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.18676824180302</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.929031696473762</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.543944920870204</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.971409815905997</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.0301692724337747</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.01565767766943406</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.03066805593407834</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.336475808721216</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-2.371033939447287</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.424419283931734</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.5283319747878767</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.01426936151318881</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.02408113948996212</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.02454866822740605</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.005608149893763953</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.74398870127168</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.325807760280249</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-8.425671950646302</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-12.0626644070805</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.04887945418117663</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.08398937741331494</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.08540828152368753</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.1268706535348672</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>8.511036167315524</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1.498120711993044</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1.402043779929575</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>18.26923905006687</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.09738670677227031</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.01536222215249154</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.01374400742882853</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.225897219489676</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.19544634363583</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.2257039938332372</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.2790954719370409</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-7.564301555855879</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.002099767370628622</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.002380002078988328</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.002963941144857743</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.08087942035495274</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.295766626965879</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.22654929962678</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.29192181874022</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-14.89986619707026</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.02455525752447291</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.02323719418969914</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.02428785319755575</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1565371693783524</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.652481378122702</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.865262728209667</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.765168831857643</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-1.216276412652926</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.0290714484288906</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.01991486773934201</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.01890476612425379</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>-0.01349791130647614</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
